--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/region-de-los-rios.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/region-de-los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4923-21-CM26</t>
+          <t>3568-98-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>13.962.630-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,616 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>2582.79</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3568-185-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2786.03</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3568-291-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>2697.34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3568-449-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>2805.66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3568-536-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>2841.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4923-83-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>10124.64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3568-557-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>3822.61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057553-1723-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>5853.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3568-742-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2717.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3568-874-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>3843.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4923-21-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>17188.63</v>
       </c>
     </row>
